--- a/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est dans la cuisine. Elle tient la tablette. Des sons sortent. Maman s'approche. Maman dit : fini. L'adulte dit fini. Aurore écoute. Elle va éteindre. Aurore éteint la tablette. L'écran devient noir. Elle pose la tablette. Maman dit : un autre jeu. Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.</t>
+          <t>Aurore est dans la cuisine. Elle tient la tablette. Des sons sortent. Maman s'approche. Fini. L'adulte dit fini. Aurore écoute. Elle va éteindre. Aurore éteint la tablette. L'écran devient noir. Elle pose la tablette. Un autre jeu. Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore est dans la cuisine. Elle tient la tablette. Des sons sortent. Maman s'approche.
+maman|Fini. L'adulte dit fini.
+narrateur|Aurore écoute. Elle va éteindre. Aurore éteint la tablette. L'écran devient noir. Elle pose la tablette.
+maman|Un autre jeu.
+narrateur|Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Aurore ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|L'adulte a dit fini. Aurore a éteint. Elle a pris un autre jeu. Les cuillères, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore range les cuillères. Papa dit merci. La cuisine est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Maman dit fini. Que fait Aurore ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|L'adulte a dit fini. Aurore a éteint. Elle a pris un autre jeu. Les cuillères, c'était bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Aurore range les cuillères. Papa dit merci. La cuisine est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurore éteint la tablette</t>
+          <t>Les cuillères en bois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le pain fait de la buée. Maman dit fini. Chouchou éteint. Toc toc, les cuillères. Ça sent le pain.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est dans la cuisine. Elle tient la tablette. Des sons sortent. Maman s'approche. Fini. L'adulte dit fini. Aurore écoute. Elle va éteindre. Aurore éteint la tablette. L'écran devient noir. Elle pose la tablette. Un autre jeu. Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.</t>
+          <t>Le pain chaud fait de la buée. La buée est sur la fenêtre. Ça sent le pain. Deux cuillères en bois attendent. Elles sont sur la table. La table est un peu collante. Une miette dorée reste au bord. Le torchon est encore un peu humide. Chouchou, tu sens le pain ? Oui, maman. Ça sent le chaud. Ça sent le four, aussi. Tu vois les cuillères ? Oui. En bois. En ce moment, Chouchou tient la tablette. Des sons sortent. C'est un petit rythme. Ça tape, maman. Oui. Un petit rythme. Maman s'approche. Fini. L'adulte dit fini. Chouchou écoute. C'est fini. On va éteindre. Chouchou va éteindre. Chouchou éteint la tablette. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. Un autre jeu. Un autre jeu. Chouchou prend les cuillères. Le bois est lisse et chaud. Toc toc, sur la table. J'arrive. Je joue avec toi. Papa tape un rythme. Chouchou tape aussi. Toc toc. Oui. Toc toc. Encore un coup ? Chouchou tape encore. La miette saute un peu. La miette saute. Oui. Tout doucement. Bravo. Tu as fait du bon travail. L'écran est éteint. Oui. Un autre jeu, c'est bien. Ça sent encore le pain chaud. La buée dessine un rond. Tu as éteint ? Oui, maman. Un autre jeu. Les cuillères. Bravo, Chouchou. La fenêtre reste un peu floue.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aurore est dans la cuisine. Elle tient la tablette. Des sons sortent. Maman s'approche.
-maman|Fini. L'adulte dit fini.
-narrateur|Aurore écoute. Elle va éteindre. Aurore éteint la tablette. L'écran devient noir. Elle pose la tablette.
+          <t>narrateur|Le pain chaud fait de la buée.
+narrateur|La buée est sur la fenêtre.
+narrateur|Ça sent le pain.
+narrateur|Deux cuillères en bois attendent.
+narrateur|Elles sont sur la table.
+narrateur|La table est un peu collante.
+narrateur|Une miette dorée reste au bord.
+narrateur|Le torchon est encore un peu humide.
+maman|Chouchou, tu sens le pain ?
+enfant-m|Oui, maman.
+enfant-m|Ça sent le chaud.
+papa|Ça sent le four, aussi.
+maman|Tu vois les cuillères ?
+enfant-m|Oui.
+enfant-m|En bois.
+narrateur|En ce moment, Chouchou tient la tablette.
+narrateur|Des sons sortent.
+narrateur|C'est un petit rythme.
+enfant-m|Ça tape, maman.
+maman|Oui.
+maman|Un petit rythme.
+narrateur|Maman s'approche.
+maman|Fini.
+narrateur|L'adulte dit fini.
+narrateur|Chouchou écoute.
+enfant-m|C'est fini.
+maman|On va éteindre.
+narrateur|Chouchou va éteindre.
+narrateur|Chouchou éteint la tablette.
+narrateur|L'écran devient noir.
+narrateur|Il pose la tablette.
+maman|Bravo, Chouchou.
+maman|Tu as éteint.
 maman|Un autre jeu.
-narrateur|Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Un autre jeu.
+narrateur|Chouchou prend les cuillères.
+narrateur|Le bois est lisse et chaud.
+narrateur|Toc toc, sur la table.
+papa|J'arrive.
+papa|Je joue avec toi.
+narrateur|Papa tape un rythme.
+narrateur|Chouchou tape aussi.
+enfant-m|Toc toc.
+papa|Oui.
+papa|Toc toc.
+maman|Encore un coup ?
+narrateur|Chouchou tape encore.
+narrateur|La miette saute un peu.
+enfant-m|La miette saute.
+papa|Oui.
+papa|Tout doucement.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-m|L'écran est éteint.
+maman|Oui.
+maman|Un autre jeu, c'est bien.
+narrateur|Ça sent encore le pain chaud.
+narrateur|La buée dessine un rond.
+maman|Tu as éteint ?
+enfant-m|Oui, maman.
+papa|Un autre jeu.
+enfant-m|Les cuillères.
+papa|Bravo, Chouchou.
+narrateur|La fenêtre reste un peu floue.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pain_chaud</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maman dit fini. Que fait Aurore ?</t>
+          <t>Maman dit fini. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maman dit fini. Que fait Aurore ?</t>
+          <t>narrateur|Maman dit fini.
+narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>L'adulte a dit fini. Aurore a éteint. Elle a pris un autre jeu. Les cuillères, c'était bien.</t>
+          <t>Maman a dit fini. L'adulte a dit fini. Chouchou a éteint. Il a pris un autre jeu. Tu as éteint ? Oui, maman. Et après ? Un autre jeu. Bravo. Les cuillères, c'était bien. Chouchou touche le bois. Le bois est lisse. On rejoue le rythme ? Toc toc. La miette reste au bord. La buée dessine encore un rond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1748,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|L'adulte a dit fini. Aurore a éteint. Elle a pris un autre jeu. Les cuillères, c'était bien.</t>
+          <t>narrateur|Maman a dit fini.
+narrateur|L'adulte a dit fini.
+narrateur|Chouchou a éteint.
+narrateur|Il a pris un autre jeu.
+maman|Tu as éteint ?
+enfant-m|Oui, maman.
+papa|Et après ?
+enfant-m|Un autre jeu.
+papa|Bravo.
+maman|Les cuillères, c'était bien.
+narrateur|Chouchou touche le bois.
+narrateur|Le bois est lisse.
+papa|On rejoue le rythme ?
+enfant-m|Toc toc.
+narrateur|La miette reste au bord.
+narrateur|La buée dessine encore un rond.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aurore range les cuillères. Papa dit merci. La cuisine est calme.</t>
+          <t>Chouchou range les cuillères. Tu as fini de ranger ? Oui, papa. Bravo. Merci. Merci, papa. Merci, maman. Merci, Chouchou. On essuie la table ? Maman essuie la table. La cuisine est calme. Le pain sent encore le chaud.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1927,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aurore range les cuillères. Papa dit merci. La cuisine est calme.</t>
+          <t>narrateur|Chouchou range les cuillères.
+papa|Tu as fini de ranger ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|Merci.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+maman|Merci, Chouchou.
+maman|On essuie la table ?
+narrateur|Maman essuie la table.
+narrateur|La cuisine est calme.
+narrateur|Le pain sent encore le chaud.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les cuillères sont rangées. L'écran est éteint. Oui. Bravo, Chouchou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2106,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les cuillères sont rangées.
+enfant-m|L'écran est éteint.
+maman|Oui.
+papa|Bravo, Chouchou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le pain chaud fait de la buée. La buée est sur la fenêtre. Ça sent le pain. Deux cuillères en bois attendent. Elles sont sur la table. La table est un peu collante. Une miette dorée reste au bord. Le torchon est encore un peu humide. Chouchou, tu sens le pain ? Oui, maman. Ça sent le chaud. Ça sent le four, aussi. Tu vois les cuillères ? Oui. En bois. En ce moment, Chouchou tient la tablette. Des sons sortent. C'est un petit rythme. Ça tape, maman. Oui. Un petit rythme. Maman s'approche. Fini. L'adulte dit fini. Chouchou écoute. C'est fini. On va éteindre. Chouchou va éteindre. Chouchou éteint la tablette. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. Un autre jeu. Un autre jeu. Chouchou prend les cuillères. Le bois est lisse et chaud. Toc toc, sur la table. J'arrive. Je joue avec toi. Papa tape un rythme. Chouchou tape aussi. Toc toc. Oui. Toc toc. Encore un coup ? Chouchou tape encore. La miette saute un peu. La miette saute. Oui. Tout doucement. Bravo. Tu as fait du bon travail. L'écran est éteint. Oui. Un autre jeu, c'est bien. Ça sent encore le pain chaud. La buée dessine un rond. Tu as éteint ? Oui, maman. Un autre jeu. Les cuillères. Bravo, Chouchou. La fenêtre reste un peu floue.</t>
+          <t>Le pain chaud fait de la buée. La buée est sur la fenêtre. Ça sent le pain. Deux cuillères en bois attendent. Elles sont sur la table. La table est un peu collante. Une miette dorée reste au bord. Le torchon est encore un peu humide. Chouchou, tu sens le pain ? Oui, maman. Ça sent le chaud. Ça sent le four, aussi. Tu vois les cuillères ? Oui. En bois. En ce moment, Chouchou tient la tablette. Des sons sortent. C'est un petit rythme. Ça tape, maman. Oui. Un petit rythme. Maman s'approche. Fini. L'adulte dit fini. Chouchou écoute. C'est fini. On va éteindre. Chouchou va éteindre. Chouchou éteint la tablette. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. Un autre jeu. Un autre jeu. Chouchou prend les cuillères. Le bois est lisse et chaud. Toc toc, sur la table. J'arrive. Je joue avec toi. Papa tape un rythme. Chouchou tape aussi. Toc toc. Oui. Toc toc. Encore un coup ? Chouchou tape encore. La miette saute un peu. La miette saute. Oui. Tout doucement. Bravo. L'écran est éteint. Oui. Un autre jeu, c'est bien. Ça sent encore le pain chaud. La buée dessine un rond. Tu as éteint ? Oui, maman. Un autre jeu. Les cuillères. Bravo, Chouchou. La fenêtre reste un peu floue.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aurore est dans la cuisine. Elle tient la tablette. Des sons sortent. Maman s'approche. Maman dit : fini. L'adulte dit fini. Aurore écoute. Elle va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Aurore éteint la tablette. L'écran devient noir. Elle pose la tablette. Maman dit : un autre jeu. Aurore prend les cuillères en bois. Toc toc sur la table. Papa arrive. Il sourit. Aurore a éteint. Elle a un autre jeu. Elles tapent un rythme. Ça sent le pain chaud.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pain chaud fait de la buée. La buée est sur la fenêtre. Ça sent le pain. Deux cuillères en bois attendent. Elles sont sur la table. La table est un peu collante. Une miette dorée reste au bord. Le torchon est encore un peu humide. Chouchou, tu sens le pain ? Oui, maman. Ça sent le chaud. Ça sent le four, aussi. Tu vois les cuillères ? Oui. En bois. En ce moment, Chouchou tient la tablette. Des sons sortent. C'est un petit rythme. Ça tape, maman. Oui. Un petit rythme. Maman s'approche. Fini. L'adulte dit fini. Chouchou écoute. C'est fini. On va éteindre. Chouchou va éteindre. Chouchou éteint la tablette. L'écran devient noir. Il pose la tablette. Bravo, Chouchou. Tu as éteint. Un autre jeu. Un autre jeu. Chouchou prend les cuillères. Le bois est lisse et chaud. Toc toc, sur la table. J'arrive. Je joue avec toi. Papa tape un rythme. Chouchou tape aussi. Toc toc. Oui. Toc toc. Encore un coup ? Chouchou tape encore. La miette saute un peu. La miette saute. Oui. Tout doucement. Bravo. L'écran est éteint. Oui. Un autre jeu, c'est bien. Ça sent encore le pain chaud. La buée dessine un rond. Tu as éteint ? Oui, maman. Un autre jeu. Les cuillères. Bravo, Chouchou. La fenêtre reste un peu floue.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1376,7 +1376,6 @@
 papa|Oui.
 papa|Tout doucement.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 enfant-m|L'écran est éteint.
 maman|Oui.
 maman|Un autre jeu, c'est bien.
@@ -1424,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman dit fini. Que fait Aurore ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman dit fini. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1578,6 @@
 narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1609,7 +1607,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;L'adulte a dit fini. Aurore a éteint. Elle a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. Les cuillères, c'était bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. L'adulte a dit fini. Chouchou a éteint. Il a pris un autre jeu. Tu as éteint ? Oui, maman. Et après ? Un autre jeu. Bravo. Les cuillères, c'était bien. Chouchou touche le bois. Le bois est lisse. On rejoue le rythme ? Toc toc. La miette reste au bord. La buée dessine encore un rond.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1766,7 +1764,6 @@
 narrateur|La buée dessine encore un rond.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1796,7 +1793,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aurore range les cuillères. Papa dit merci. La cuisine est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou range les cuillères. Tu as fini de ranger ? Oui, papa. Bravo. Merci. Merci, papa. Merci, maman. Merci, Chouchou. On essuie la table ? Maman essuie la table. La cuisine est calme. Le pain sent encore le chaud.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,7 +1938,6 @@
 narrateur|Le pain sent encore le chaud.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les cuillères sont rangées. L'écran est éteint. Oui. Bravo, Chouchou. L'histoire est finie.</t>
+          <t>Les cuillères sont rangées. L'écran est éteint. Oui. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les cuillères sont rangées. L'écran est éteint. Oui. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,11 +2105,9 @@
           <t>narrateur|Les cuillères sont rangées.
 enfant-m|L'écran est éteint.
 maman|Oui.
-papa|Bravo, Chouchou.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Chouchou.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-10.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, pain chaud, cuillères en bois</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurore, maman, papa</t>
+          <t>Chouchou, maman, papa</t>
         </is>
       </c>
     </row>
